--- a/TestNG_Selenium_Project/TestData/TutorialsNinja_RegisterUserData.xlsx
+++ b/TestNG_Selenium_Project/TestData/TutorialsNinja_RegisterUserData.xlsx
@@ -38,7 +38,7 @@
     <t>Selenium</t>
   </si>
   <si>
-    <t>testselenium0123456789@gmail.com</t>
+    <t>testselenium02@gmail.com</t>
   </si>
   <si>
     <t>9876543210</t>
